--- a/data/bulk-upload-users/upload-users-valid.xlsx
+++ b/data/bulk-upload-users/upload-users-valid.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{664A0F8A-72AD-4208-9DDC-EE092A6CA92E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8952A6CA-FC39-4807-9E24-0CEE824AB9FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -15,10 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
-  <si>
-    <t>no</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="13">
   <si>
     <t>firstName</t>
   </si>
@@ -41,20 +38,29 @@
     <t>NID</t>
   </si>
   <si>
-    <t>Panha</t>
-  </si>
-  <si>
-    <t>ID0011223ABCD</t>
-  </si>
-  <si>
-    <t>0971234567</t>
+    <t>remark:</t>
+  </si>
+  <si>
+    <t>PASSPORT</t>
+  </si>
+  <si>
+    <t>David</t>
+  </si>
+  <si>
+    <t>123456789</t>
+  </si>
+  <si>
+    <t>ID00112233ABC</t>
+  </si>
+  <si>
+    <t>092234234</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -67,6 +73,11 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -89,9 +100,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -431,67 +445,103 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.109375" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>1</v>
       </c>
       <c r="B2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" t="s">
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2"/>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1</v>
+      </c>
+      <c r="C5" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" t="s">
+        <v>3</v>
+      </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
+      <c r="F5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>6</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="1">
-        <v>0</v>
-      </c>
-      <c r="E2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G3" s="1"/>
+      <c r="E7" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" t="s">
+        <v>12</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:A3"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <dataValidations count="1">
+    <dataValidation type="list" showErrorMessage="1" errorTitle="Invalid Value" error="Please select from dropdown only." sqref="D6:D100" xr:uid="{2D13F685-B72A-4076-827B-8588CB09E043}">
+      <formula1>"PASSPORT,NID"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
 </worksheet>
